--- a/projects/2024/bus_performance_analysis/bus_perfomance_comparison.xlsx
+++ b/projects/2024/bus_performance_analysis/bus_perfomance_comparison.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahasan\Documents\Workshop\Archived Projects\Bus Performance Analysis\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahasan\Documents\RStudio\teito7000.github.io\projects\2024\bus_performance_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96B71BAD-ACDB-4DA5-BDDE-A83431F6B6E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A4A58C1-6A2A-4685-845B-23C186DA43E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{830AABF1-BEEF-43AA-8902-734A9CDECEEB}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{830AABF1-BEEF-43AA-8902-734A9CDECEEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$73</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -209,12 +212,6 @@
     <t>number_of_stops</t>
   </si>
   <si>
-    <t>average_scheduled_speed</t>
-  </si>
-  <si>
-    <t>average_stop_distance</t>
-  </si>
-  <si>
     <t>route_length</t>
   </si>
   <si>
@@ -234,6 +231,12 @@
   </si>
   <si>
     <t>Keefer Place</t>
+  </si>
+  <si>
+    <t>average_scheduled_speed_km/h</t>
+  </si>
+  <si>
+    <t>average_stop_distance_m</t>
   </si>
 </sst>
 </file>
@@ -411,9 +414,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -451,7 +454,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -557,7 +560,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -699,7 +702,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -707,18 +710,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{972E81A3-D75E-46E6-82F0-4D32CA77E236}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.85546875" customWidth="1"/>
-    <col min="7" max="7" width="17.85546875" customWidth="1"/>
-    <col min="8" max="8" width="18.85546875" customWidth="1"/>
-    <col min="9" max="9" width="33.42578125" customWidth="1"/>
-    <col min="10" max="10" width="27.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.85546875" style="11" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.28515625" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="26.7109375" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="28.140625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="21.28515625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="17.140625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="29" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.7109375" style="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="9" customFormat="1" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -738,25 +744,25 @@
         <v>55</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>56</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K1" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="K1" s="10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>49</v>
       </c>
@@ -793,7 +799,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>49</v>
       </c>
@@ -830,7 +836,7 @@
         <v>0.90400000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -867,7 +873,7 @@
         <v>0.93700000000000006</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>49</v>
       </c>
@@ -904,7 +910,7 @@
         <v>0.90400000000000003</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>49</v>
       </c>
@@ -941,7 +947,7 @@
         <v>0.80800000000000005</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>49</v>
       </c>
@@ -978,7 +984,7 @@
         <v>0.81499999999999995</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>49</v>
       </c>
@@ -1015,7 +1021,7 @@
         <v>0.80300000000000005</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>49</v>
       </c>
@@ -1052,7 +1058,7 @@
         <v>0.80200000000000005</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>49</v>
       </c>
@@ -1089,7 +1095,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>49</v>
       </c>
@@ -1126,7 +1132,7 @@
         <v>0.82399999999999995</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>49</v>
       </c>
@@ -1163,7 +1169,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>49</v>
       </c>
@@ -1171,7 +1177,7 @@
         <v>48</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D13" t="s">
         <v>23</v>
@@ -1200,7 +1206,7 @@
         <v>0.83399999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>49</v>
       </c>
@@ -1237,7 +1243,7 @@
         <v>0.71499999999999997</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>49</v>
       </c>
@@ -1274,7 +1280,7 @@
         <v>0.84599999999999997</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>49</v>
       </c>
@@ -1311,7 +1317,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>49</v>
       </c>
@@ -1348,7 +1354,7 @@
         <v>0.85199999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>49</v>
       </c>
@@ -1385,7 +1391,7 @@
         <v>0.85199999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1422,7 +1428,7 @@
         <v>0.746</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>49</v>
       </c>
@@ -1459,7 +1465,7 @@
         <v>0.85399999999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1496,7 +1502,7 @@
         <v>0.76400000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>49</v>
       </c>
@@ -1533,7 +1539,7 @@
         <v>0.77800000000000002</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -1570,7 +1576,7 @@
         <v>0.76900000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>49</v>
       </c>
@@ -1607,7 +1613,7 @@
         <v>0.79300000000000004</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>49</v>
       </c>
@@ -1644,7 +1650,7 @@
         <v>0.77700000000000002</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>49</v>
       </c>
@@ -1681,7 +1687,7 @@
         <v>0.76700000000000002</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>49</v>
       </c>
@@ -1718,7 +1724,7 @@
         <v>0.878</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>49</v>
       </c>
@@ -1755,7 +1761,7 @@
         <v>0.71199999999999997</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>49</v>
       </c>
@@ -1792,7 +1798,7 @@
         <v>0.78200000000000003</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>49</v>
       </c>
@@ -1829,7 +1835,7 @@
         <v>0.84399999999999997</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>49</v>
       </c>
@@ -1837,10 +1843,10 @@
         <v>48</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D31" t="s">
         <v>63</v>
-      </c>
-      <c r="D31" t="s">
-        <v>65</v>
       </c>
       <c r="E31" t="s">
         <v>28</v>
@@ -1866,7 +1872,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>49</v>
       </c>
@@ -1903,7 +1909,7 @@
         <v>0.79200000000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>49</v>
       </c>
@@ -1940,7 +1946,7 @@
         <v>0.70699999999999996</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>49</v>
       </c>
@@ -1977,7 +1983,7 @@
         <v>0.78900000000000003</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>49</v>
       </c>
@@ -2014,7 +2020,7 @@
         <v>0.81</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>49</v>
       </c>
@@ -2051,7 +2057,7 @@
         <v>0.72299999999999998</v>
       </c>
     </row>
-    <row r="37" spans="1:11" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" s="4" customFormat="1" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>49</v>
       </c>
@@ -2062,7 +2068,7 @@
         <v>503</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>33</v>
@@ -2097,33 +2103,33 @@
         <v>46</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D38" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E38" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F38">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G38">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H38">
-        <v>10800</v>
+        <v>17200</v>
       </c>
       <c r="I38" s="3">
-        <f t="shared" si="0"/>
-        <v>17.052631578947366</v>
+        <f>($H38/($F38*60))*3.6</f>
+        <v>28.666666666666668</v>
       </c>
       <c r="J38" s="6">
-        <f t="shared" si="1"/>
-        <v>981.81818181818187</v>
+        <f>$H38/$G38</f>
+        <v>2457.1428571428573</v>
       </c>
       <c r="K38" s="11">
-        <v>0.85</v>
+        <v>0.93700000000000006</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -2134,30 +2140,30 @@
         <v>46</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D39" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E39" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F39">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G39">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H39">
-        <v>10100</v>
+        <v>18900</v>
       </c>
       <c r="I39" s="3">
-        <f t="shared" si="0"/>
-        <v>14.428571428571429</v>
+        <f>($H39/($F39*60))*3.6</f>
+        <v>25.2</v>
       </c>
       <c r="J39" s="6">
-        <f t="shared" si="1"/>
-        <v>1122.2222222222222</v>
+        <f>$H39/$G39</f>
+        <v>1181.25</v>
       </c>
       <c r="K39" s="11">
         <v>0.90400000000000003</v>
@@ -2168,36 +2174,37 @@
         <v>50</v>
       </c>
       <c r="B40" t="s">
-        <v>46</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>6</v>
+        <v>48</v>
+      </c>
+      <c r="C40" s="2">
+        <v>503</v>
       </c>
       <c r="D40" t="s">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="E40" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F40">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="G40">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="H40">
-        <v>17200</v>
+        <f>32.8*1000</f>
+        <v>32800</v>
       </c>
       <c r="I40" s="3">
-        <f t="shared" si="0"/>
-        <v>28.666666666666668</v>
+        <f>($H40/($F40*60))*3.6</f>
+        <v>24.599999999999998</v>
       </c>
       <c r="J40" s="6">
-        <f t="shared" si="1"/>
-        <v>2457.1428571428573</v>
-      </c>
-      <c r="K40" s="11">
-        <v>0.93700000000000006</v>
+        <f>$H40/$G40</f>
+        <v>780.95238095238096</v>
+      </c>
+      <c r="K40" s="13">
+        <v>0.82199999999999995</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -2205,36 +2212,36 @@
         <v>50</v>
       </c>
       <c r="B41" t="s">
-        <v>46</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>9</v>
+        <v>48</v>
+      </c>
+      <c r="C41" s="2">
+        <v>410</v>
       </c>
       <c r="D41" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E41" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F41">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="G41">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="H41">
-        <v>18900</v>
+        <v>21500</v>
       </c>
       <c r="I41" s="3">
-        <f t="shared" si="0"/>
-        <v>25.2</v>
+        <f>($H41/($F41*60))*3.6</f>
+        <v>21.147540983606557</v>
       </c>
       <c r="J41" s="6">
-        <f t="shared" si="1"/>
-        <v>1181.25</v>
+        <f>$H41/$G41</f>
+        <v>614.28571428571433</v>
       </c>
       <c r="K41" s="11">
-        <v>0.90400000000000003</v>
+        <v>0.76400000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -2242,36 +2249,36 @@
         <v>50</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>12</v>
+        <v>47</v>
+      </c>
+      <c r="C42" s="2">
+        <v>99</v>
       </c>
       <c r="D42" t="s">
+        <v>15</v>
+      </c>
+      <c r="E42" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42">
+        <v>41</v>
+      </c>
+      <c r="G42">
         <v>13</v>
       </c>
-      <c r="E42" t="s">
-        <v>14</v>
-      </c>
-      <c r="F42">
-        <v>55</v>
-      </c>
-      <c r="G42">
-        <v>15</v>
-      </c>
       <c r="H42">
-        <v>17800</v>
+        <v>14100</v>
       </c>
       <c r="I42" s="3">
-        <f t="shared" si="0"/>
-        <v>19.418181818181818</v>
+        <f>($H42/($F42*60))*3.6</f>
+        <v>20.634146341463413</v>
       </c>
       <c r="J42" s="6">
-        <f t="shared" si="1"/>
-        <v>1186.6666666666667</v>
-      </c>
-      <c r="K42" s="13">
-        <v>0.80800000000000005</v>
+        <f>$H42/$G42</f>
+        <v>1084.6153846153845</v>
+      </c>
+      <c r="K42" s="11">
+        <v>0.81499999999999995</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -2279,36 +2286,36 @@
         <v>50</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C43" s="2">
-        <v>99</v>
+        <v>321</v>
       </c>
       <c r="D43" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E43" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="F43">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="G43">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="H43">
-        <v>14100</v>
+        <v>21000</v>
       </c>
       <c r="I43" s="3">
-        <f t="shared" si="0"/>
-        <v>20.634146341463413</v>
+        <f>($H43/($F43*60))*3.6</f>
+        <v>20</v>
       </c>
       <c r="J43" s="6">
-        <f t="shared" si="1"/>
-        <v>1084.6153846153845</v>
+        <f>$H43/$G43</f>
+        <v>437.5</v>
       </c>
       <c r="K43" s="11">
-        <v>0.81499999999999995</v>
+        <v>0.71199999999999997</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -2319,33 +2326,33 @@
         <v>48</v>
       </c>
       <c r="C44" s="2">
-        <v>49</v>
+        <v>430</v>
       </c>
       <c r="D44" t="s">
         <v>16</v>
       </c>
       <c r="E44" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F44">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="G44">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="H44">
-        <v>20500</v>
+        <v>18600</v>
       </c>
       <c r="I44" s="3">
-        <f t="shared" si="0"/>
-        <v>19.21875</v>
+        <f>($H44/($F44*60))*3.6</f>
+        <v>19.928571428571427</v>
       </c>
       <c r="J44" s="6">
-        <f t="shared" si="1"/>
-        <v>336.06557377049182</v>
+        <f>$H44/$G44</f>
+        <v>845.4545454545455</v>
       </c>
       <c r="K44" s="11">
-        <v>0.80300000000000005</v>
+        <v>0.72299999999999998</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -2356,33 +2363,33 @@
         <v>48</v>
       </c>
       <c r="C45" s="2">
-        <v>319</v>
+        <v>84</v>
       </c>
       <c r="D45" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="E45" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F45">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="G45">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="H45">
-        <v>12000</v>
+        <v>13700</v>
       </c>
       <c r="I45" s="3">
-        <f t="shared" si="0"/>
-        <v>14.117647058823529</v>
+        <f>($H45/($F45*60))*3.6</f>
+        <v>19.571428571428573</v>
       </c>
       <c r="J45" s="6">
-        <f t="shared" si="1"/>
-        <v>444.44444444444446</v>
+        <f>$H45/$G45</f>
+        <v>761.11111111111109</v>
       </c>
       <c r="K45" s="11">
-        <v>0.80200000000000005</v>
+        <v>0.78900000000000003</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -2390,36 +2397,36 @@
         <v>50</v>
       </c>
       <c r="B46" t="s">
-        <v>48</v>
-      </c>
-      <c r="C46" s="2">
-        <v>25</v>
+        <v>46</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="D46" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E46" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F46">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="G46">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="H46">
-        <v>22400</v>
+        <v>17800</v>
       </c>
       <c r="I46" s="3">
-        <f t="shared" si="0"/>
-        <v>17.920000000000002</v>
+        <f>($H46/($F46*60))*3.6</f>
+        <v>19.418181818181818</v>
       </c>
       <c r="J46" s="6">
-        <f t="shared" si="1"/>
-        <v>350</v>
-      </c>
-      <c r="K46" s="11">
-        <v>0.83</v>
+        <f>$H46/$G46</f>
+        <v>1186.6666666666667</v>
+      </c>
+      <c r="K46" s="13">
+        <v>0.80800000000000005</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -2430,33 +2437,33 @@
         <v>48</v>
       </c>
       <c r="C47" s="2">
+        <v>49</v>
+      </c>
+      <c r="D47" t="s">
         <v>16</v>
       </c>
-      <c r="D47" t="s">
-        <v>19</v>
-      </c>
       <c r="E47" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F47">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="G47">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="H47">
         <v>20500</v>
       </c>
       <c r="I47" s="3">
-        <f t="shared" si="0"/>
-        <v>13.820224719101123</v>
+        <f>($H47/($F47*60))*3.6</f>
+        <v>19.21875</v>
       </c>
       <c r="J47" s="6">
-        <f t="shared" si="1"/>
-        <v>277.02702702702703</v>
+        <f>$H47/$G47</f>
+        <v>336.06557377049182</v>
       </c>
       <c r="K47" s="11">
-        <v>0.82399999999999995</v>
+        <v>0.80300000000000005</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
@@ -2467,33 +2474,33 @@
         <v>48</v>
       </c>
       <c r="C48" s="2">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D48" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E48" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F48">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="G48">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="H48">
-        <v>9800</v>
+        <v>17900</v>
       </c>
       <c r="I48" s="3">
-        <f t="shared" si="0"/>
-        <v>8.28169014084507</v>
+        <f>($H48/($F48*60))*3.6</f>
+        <v>18.842105263157897</v>
       </c>
       <c r="J48" s="6">
-        <f t="shared" si="1"/>
-        <v>192.15686274509804</v>
+        <f>$H48/$G48</f>
+        <v>406.81818181818181</v>
       </c>
       <c r="K48" s="11">
-        <v>0.8</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -2503,34 +2510,34 @@
       <c r="B49" t="s">
         <v>48</v>
       </c>
-      <c r="C49" s="14" t="s">
-        <v>64</v>
+      <c r="C49" s="2">
+        <v>100</v>
       </c>
       <c r="D49" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E49" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F49">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G49">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="H49">
-        <v>6500</v>
+        <v>15400</v>
       </c>
       <c r="I49" s="3">
-        <f t="shared" si="0"/>
-        <v>8.1250000000000018</v>
+        <f>($H49/($F49*60))*3.6</f>
+        <v>18.48</v>
       </c>
       <c r="J49" s="6">
-        <f t="shared" si="1"/>
-        <v>232.14285714285714</v>
+        <f>$H49/$G49</f>
+        <v>358.13953488372096</v>
       </c>
       <c r="K49" s="11">
-        <v>0.83399999999999996</v>
+        <v>0.85199999999999998</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -2541,33 +2548,33 @@
         <v>48</v>
       </c>
       <c r="C50" s="2">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D50" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E50" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F50">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G50">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="H50">
-        <v>13400</v>
+        <v>22400</v>
       </c>
       <c r="I50" s="3">
-        <f t="shared" si="0"/>
-        <v>10.864864864864865</v>
+        <f>($H50/($F50*60))*3.6</f>
+        <v>17.920000000000002</v>
       </c>
       <c r="J50" s="6">
-        <f t="shared" si="1"/>
-        <v>231.0344827586207</v>
+        <f>$H50/$G50</f>
+        <v>350</v>
       </c>
       <c r="K50" s="11">
-        <v>0.71499999999999997</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -2575,36 +2582,36 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>48</v>
-      </c>
-      <c r="C51" s="2">
-        <v>9</v>
+        <v>46</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="D51" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E51" t="s">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="F51">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="G51">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="H51">
-        <v>10500</v>
+        <v>10800</v>
       </c>
       <c r="I51" s="3">
-        <f t="shared" si="0"/>
-        <v>12.352941176470587</v>
+        <f>($H51/($F51*60))*3.6</f>
+        <v>17.052631578947366</v>
       </c>
       <c r="J51" s="6">
-        <f t="shared" si="1"/>
-        <v>244.18604651162789</v>
+        <f>$H51/$G51</f>
+        <v>981.81818181818187</v>
       </c>
       <c r="K51" s="11">
-        <v>0.84599999999999997</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -2615,33 +2622,33 @@
         <v>48</v>
       </c>
       <c r="C52" s="2">
-        <v>3</v>
+        <v>130</v>
       </c>
       <c r="D52" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="E52" t="s">
+        <v>16</v>
+      </c>
+      <c r="F52">
+        <v>44</v>
+      </c>
+      <c r="G52">
         <v>28</v>
       </c>
-      <c r="F52">
-        <v>56</v>
-      </c>
-      <c r="G52">
-        <v>38</v>
-      </c>
       <c r="H52">
-        <v>10000</v>
+        <v>11800</v>
       </c>
       <c r="I52" s="3">
-        <f t="shared" si="0"/>
-        <v>10.714285714285715</v>
+        <f>($H52/($F52*60))*3.6</f>
+        <v>16.09090909090909</v>
       </c>
       <c r="J52" s="6">
-        <f t="shared" si="1"/>
-        <v>263.15789473684208</v>
+        <f>$H52/$G52</f>
+        <v>421.42857142857144</v>
       </c>
       <c r="K52" s="11">
-        <v>0.75</v>
+        <v>0.78200000000000003</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -2652,33 +2659,33 @@
         <v>48</v>
       </c>
       <c r="C53" s="2">
-        <v>2</v>
+        <v>240</v>
       </c>
       <c r="D53" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="E53" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F53">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="G53">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H53">
-        <v>8600</v>
+        <v>12500</v>
       </c>
       <c r="I53" s="3">
-        <f t="shared" si="0"/>
-        <v>13.578947368421053</v>
+        <f>($H53/($F53*60))*3.6</f>
+        <v>15.306122448979592</v>
       </c>
       <c r="J53" s="6">
-        <f t="shared" si="1"/>
-        <v>286.66666666666669</v>
+        <f>$H53/$G53</f>
+        <v>320.5128205128205</v>
       </c>
       <c r="K53" s="11">
-        <v>0.85199999999999998</v>
+        <v>0.76700000000000002</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -2686,36 +2693,36 @@
         <v>50</v>
       </c>
       <c r="B54" t="s">
-        <v>48</v>
-      </c>
-      <c r="C54" s="2">
-        <v>100</v>
+        <v>46</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="D54" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="E54" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="F54">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="G54">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="H54">
-        <v>15400</v>
+        <v>10100</v>
       </c>
       <c r="I54" s="3">
-        <f t="shared" si="0"/>
-        <v>18.48</v>
+        <f>($H54/($F54*60))*3.6</f>
+        <v>14.428571428571429</v>
       </c>
       <c r="J54" s="6">
-        <f t="shared" si="1"/>
-        <v>358.13953488372096</v>
+        <f>$H54/$G54</f>
+        <v>1122.2222222222222</v>
       </c>
       <c r="K54" s="11">
-        <v>0.85199999999999998</v>
+        <v>0.90400000000000003</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -2726,33 +2733,33 @@
         <v>48</v>
       </c>
       <c r="C55" s="2">
-        <v>7</v>
+        <v>319</v>
       </c>
       <c r="D55" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="E55" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="F55">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="G55">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="H55">
-        <v>15700</v>
+        <v>12000</v>
       </c>
       <c r="I55" s="3">
-        <f t="shared" si="0"/>
-        <v>11.487804878048781</v>
+        <f>($H55/($F55*60))*3.6</f>
+        <v>14.117647058823529</v>
       </c>
       <c r="J55" s="6">
-        <f t="shared" si="1"/>
-        <v>249.20634920634922</v>
+        <f>$H55/$G55</f>
+        <v>444.44444444444446</v>
       </c>
       <c r="K55" s="11">
-        <v>0.746</v>
+        <v>0.80200000000000005</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -2763,33 +2770,33 @@
         <v>48</v>
       </c>
       <c r="C56" s="2">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="D56" t="s">
+        <v>2</v>
+      </c>
+      <c r="E56" t="s">
         <v>33</v>
       </c>
-      <c r="E56" t="s">
-        <v>2</v>
-      </c>
       <c r="F56">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G56">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="H56">
-        <v>10300</v>
+        <v>13400</v>
       </c>
       <c r="I56" s="3">
-        <f t="shared" si="0"/>
-        <v>13.434782608695652</v>
+        <f>($H56/($F56*60))*3.6</f>
+        <v>14.105263157894736</v>
       </c>
       <c r="J56" s="6">
-        <f t="shared" si="1"/>
-        <v>302.94117647058823</v>
+        <f>$H56/$G56</f>
+        <v>268</v>
       </c>
       <c r="K56" s="11">
-        <v>0.85399999999999998</v>
+        <v>0.79300000000000004</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -2800,33 +2807,33 @@
         <v>48</v>
       </c>
       <c r="C57" s="2">
-        <v>410</v>
+        <v>16</v>
       </c>
       <c r="D57" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E57" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F57">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="G57">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="H57">
-        <v>21500</v>
+        <v>20500</v>
       </c>
       <c r="I57" s="3">
-        <f t="shared" si="0"/>
-        <v>21.147540983606557</v>
+        <f>($H57/($F57*60))*3.6</f>
+        <v>13.820224719101123</v>
       </c>
       <c r="J57" s="6">
-        <f t="shared" si="1"/>
-        <v>614.28571428571433</v>
+        <f>$H57/$G57</f>
+        <v>277.02702702702703</v>
       </c>
       <c r="K57" s="11">
-        <v>0.76400000000000001</v>
+        <v>0.82399999999999995</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -2837,33 +2844,33 @@
         <v>48</v>
       </c>
       <c r="C58" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D58" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="E58" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F58">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G58">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="H58">
-        <v>8900</v>
+        <v>8600</v>
       </c>
       <c r="I58" s="3">
-        <f t="shared" si="0"/>
-        <v>10.680000000000001</v>
+        <f>($H58/($F58*60))*3.6</f>
+        <v>13.578947368421053</v>
       </c>
       <c r="J58" s="6">
-        <f t="shared" si="1"/>
-        <v>211.9047619047619</v>
+        <f>$H58/$G58</f>
+        <v>286.66666666666669</v>
       </c>
       <c r="K58" s="11">
-        <v>0.77800000000000002</v>
+        <v>0.85199999999999998</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -2874,33 +2881,33 @@
         <v>48</v>
       </c>
       <c r="C59" s="2">
+        <v>22</v>
+      </c>
+      <c r="D59" t="s">
+        <v>42</v>
+      </c>
+      <c r="E59" t="s">
         <v>14</v>
       </c>
-      <c r="D59" t="s">
-        <v>36</v>
-      </c>
-      <c r="E59" t="s">
-        <v>11</v>
-      </c>
       <c r="F59">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="G59">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="H59">
-        <v>13200</v>
+        <v>10400</v>
       </c>
       <c r="I59" s="3">
-        <f t="shared" si="0"/>
-        <v>9.9</v>
+        <f>($H59/($F59*60))*3.6</f>
+        <v>13.565217391304348</v>
       </c>
       <c r="J59" s="6">
-        <f t="shared" si="1"/>
-        <v>231.57894736842104</v>
+        <f>$H59/$G59</f>
+        <v>231.11111111111111</v>
       </c>
       <c r="K59" s="11">
-        <v>0.76900000000000002</v>
+        <v>0.84399999999999997</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -2911,33 +2918,33 @@
         <v>48</v>
       </c>
       <c r="C60" s="2">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="D60" t="s">
+        <v>33</v>
+      </c>
+      <c r="E60" t="s">
         <v>2</v>
       </c>
-      <c r="E60" t="s">
-        <v>33</v>
-      </c>
       <c r="F60">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G60">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="H60">
-        <v>13400</v>
+        <v>10300</v>
       </c>
       <c r="I60" s="3">
-        <f t="shared" si="0"/>
-        <v>14.105263157894736</v>
+        <f>($H60/($F60*60))*3.6</f>
+        <v>13.434782608695652</v>
       </c>
       <c r="J60" s="6">
-        <f t="shared" si="1"/>
-        <v>268</v>
+        <f>$H60/$G60</f>
+        <v>302.94117647058823</v>
       </c>
       <c r="K60" s="11">
-        <v>0.79300000000000004</v>
+        <v>0.85399999999999998</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -2947,34 +2954,34 @@
       <c r="B61" t="s">
         <v>48</v>
       </c>
-      <c r="C61" s="2">
-        <v>10</v>
+      <c r="C61" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="D61" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="E61" t="s">
         <v>28</v>
       </c>
       <c r="F61">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G61">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H61">
-        <v>10500</v>
+        <v>13600</v>
       </c>
       <c r="I61" s="3">
-        <f t="shared" si="0"/>
-        <v>11.05263157894737</v>
+        <f>($H61/($F61*60))*3.6</f>
+        <v>12.952380952380953</v>
       </c>
       <c r="J61" s="6">
-        <f t="shared" si="1"/>
-        <v>233.33333333333334</v>
+        <f>$H61/$G61</f>
+        <v>323.8095238095238</v>
       </c>
       <c r="K61" s="11">
-        <v>0.77700000000000002</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
@@ -2985,33 +2992,33 @@
         <v>48</v>
       </c>
       <c r="C62" s="2">
-        <v>240</v>
+        <v>9</v>
       </c>
       <c r="D62" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E62" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="F62">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G62">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H62">
-        <v>12500</v>
+        <v>10500</v>
       </c>
       <c r="I62" s="3">
-        <f t="shared" si="0"/>
-        <v>15.306122448979592</v>
+        <f>($H62/($F62*60))*3.6</f>
+        <v>12.352941176470587</v>
       </c>
       <c r="J62" s="6">
-        <f t="shared" si="1"/>
-        <v>320.5128205128205</v>
+        <f>$H62/$G62</f>
+        <v>244.18604651162789</v>
       </c>
       <c r="K62" s="11">
-        <v>0.76700000000000002</v>
+        <v>0.84599999999999997</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -3022,33 +3029,33 @@
         <v>48</v>
       </c>
       <c r="C63" s="2">
-        <v>106</v>
+        <v>4</v>
       </c>
       <c r="D63" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E63" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F63">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="G63">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="H63">
-        <v>6000</v>
+        <v>14200</v>
       </c>
       <c r="I63" s="3">
-        <f t="shared" si="0"/>
-        <v>11.25</v>
+        <f>($H63/($F63*60))*3.6</f>
+        <v>12.347826086956523</v>
       </c>
       <c r="J63" s="6">
-        <f t="shared" si="1"/>
-        <v>272.72727272727275</v>
+        <f>$H63/$G63</f>
+        <v>273.07692307692309</v>
       </c>
       <c r="K63" s="11">
-        <v>0.878</v>
+        <v>0.79200000000000004</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -3059,33 +3066,33 @@
         <v>48</v>
       </c>
       <c r="C64" s="2">
-        <v>321</v>
+        <v>7</v>
       </c>
       <c r="D64" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E64" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="F64">
+        <v>82</v>
+      </c>
+      <c r="G64">
         <v>63</v>
       </c>
-      <c r="G64">
-        <v>48</v>
-      </c>
       <c r="H64">
-        <v>21000</v>
+        <v>15700</v>
       </c>
       <c r="I64" s="3">
-        <f t="shared" si="0"/>
-        <v>20</v>
+        <f>($H64/($F64*60))*3.6</f>
+        <v>11.487804878048781</v>
       </c>
       <c r="J64" s="6">
-        <f t="shared" si="1"/>
-        <v>437.5</v>
+        <f>$H64/$G64</f>
+        <v>249.20634920634922</v>
       </c>
       <c r="K64" s="11">
-        <v>0.71199999999999997</v>
+        <v>0.746</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -3096,33 +3103,33 @@
         <v>48</v>
       </c>
       <c r="C65" s="2">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="D65" t="s">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="E65" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="F65">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G65">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H65">
-        <v>11800</v>
+        <v>6000</v>
       </c>
       <c r="I65" s="3">
-        <f t="shared" si="0"/>
-        <v>16.09090909090909</v>
+        <f>($H65/($F65*60))*3.6</f>
+        <v>11.25</v>
       </c>
       <c r="J65" s="6">
-        <f t="shared" si="1"/>
-        <v>421.42857142857144</v>
+        <f>$H65/$G65</f>
+        <v>272.72727272727275</v>
       </c>
       <c r="K65" s="11">
-        <v>0.78200000000000003</v>
+        <v>0.878</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -3133,33 +3140,33 @@
         <v>48</v>
       </c>
       <c r="C66" s="2">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D66" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E66" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F66">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G66">
         <v>45</v>
       </c>
       <c r="H66">
-        <v>10400</v>
+        <v>10500</v>
       </c>
       <c r="I66" s="3">
-        <f t="shared" si="0"/>
-        <v>13.565217391304348</v>
+        <f>($H66/($F66*60))*3.6</f>
+        <v>11.05263157894737</v>
       </c>
       <c r="J66" s="6">
-        <f t="shared" si="1"/>
-        <v>231.11111111111111</v>
+        <f>$H66/$G66</f>
+        <v>233.33333333333334</v>
       </c>
       <c r="K66" s="11">
-        <v>0.84399999999999997</v>
+        <v>0.77700000000000002</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -3169,34 +3176,34 @@
       <c r="B67" t="s">
         <v>48</v>
       </c>
-      <c r="C67" s="2" t="s">
-        <v>63</v>
+      <c r="C67" s="2">
+        <v>19</v>
       </c>
       <c r="D67" t="s">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="E67" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F67">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="G67">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="H67">
-        <v>13600</v>
+        <v>13400</v>
       </c>
       <c r="I67" s="3">
-        <f t="shared" si="0"/>
-        <v>12.952380952380953</v>
+        <f>($H67/($F67*60))*3.6</f>
+        <v>10.864864864864865</v>
       </c>
       <c r="J67" s="6">
-        <f t="shared" si="1"/>
-        <v>323.8095238095238</v>
+        <f>$H67/$G67</f>
+        <v>231.0344827586207</v>
       </c>
       <c r="K67" s="11">
-        <v>0.8</v>
+        <v>0.71499999999999997</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -3207,33 +3214,33 @@
         <v>48</v>
       </c>
       <c r="C68" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D68" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="E68" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F68">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="G68">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="H68">
-        <v>14200</v>
+        <v>10000</v>
       </c>
       <c r="I68" s="3">
-        <f t="shared" ref="I68:I73" si="2">($H68/($F68*60))*3.6</f>
-        <v>12.347826086956523</v>
+        <f>($H68/($F68*60))*3.6</f>
+        <v>10.714285714285715</v>
       </c>
       <c r="J68" s="6">
-        <f t="shared" ref="J68:J71" si="3">$H68/$G68</f>
-        <v>273.07692307692309</v>
+        <f>$H68/$G68</f>
+        <v>263.15789473684208</v>
       </c>
       <c r="K68" s="11">
-        <v>0.79200000000000004</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -3244,33 +3251,33 @@
         <v>48</v>
       </c>
       <c r="C69" s="2">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D69" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="E69" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F69">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="G69">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H69">
-        <v>10600</v>
+        <v>8900</v>
       </c>
       <c r="I69" s="3">
-        <f t="shared" si="2"/>
-        <v>9.4925373134328375</v>
+        <f>($H69/($F69*60))*3.6</f>
+        <v>10.680000000000001</v>
       </c>
       <c r="J69" s="6">
-        <f t="shared" si="3"/>
-        <v>286.48648648648651</v>
+        <f>$H69/$G69</f>
+        <v>211.9047619047619</v>
       </c>
       <c r="K69" s="11">
-        <v>0.70699999999999996</v>
+        <v>0.77800000000000002</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -3281,33 +3288,33 @@
         <v>48</v>
       </c>
       <c r="C70" s="2">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="D70" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E70" t="s">
         <v>11</v>
       </c>
       <c r="F70">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="G70">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="H70">
-        <v>13700</v>
+        <v>13200</v>
       </c>
       <c r="I70" s="3">
-        <f t="shared" si="2"/>
-        <v>19.571428571428573</v>
+        <f>($H70/($F70*60))*3.6</f>
+        <v>9.9</v>
       </c>
       <c r="J70" s="6">
-        <f t="shared" si="3"/>
-        <v>761.11111111111109</v>
+        <f>$H70/$G70</f>
+        <v>231.57894736842104</v>
       </c>
       <c r="K70" s="11">
-        <v>0.78900000000000003</v>
+        <v>0.76900000000000002</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -3318,33 +3325,33 @@
         <v>48</v>
       </c>
       <c r="C71" s="2">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="D71" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="E71" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F71">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="G71">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H71">
-        <v>17900</v>
+        <v>10600</v>
       </c>
       <c r="I71" s="3">
-        <f t="shared" si="2"/>
-        <v>18.842105263157897</v>
+        <f>($H71/($F71*60))*3.6</f>
+        <v>9.4925373134328375</v>
       </c>
       <c r="J71" s="6">
-        <f t="shared" si="3"/>
-        <v>406.81818181818181</v>
+        <f>$H71/$G71</f>
+        <v>286.48648648648651</v>
       </c>
       <c r="K71" s="11">
-        <v>0.81</v>
+        <v>0.70699999999999996</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -3355,33 +3362,33 @@
         <v>48</v>
       </c>
       <c r="C72" s="2">
-        <v>430</v>
+        <v>20</v>
       </c>
       <c r="D72" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E72" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F72">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G72">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="H72">
-        <v>18600</v>
+        <v>9800</v>
       </c>
       <c r="I72" s="3">
-        <f t="shared" si="2"/>
-        <v>19.928571428571427</v>
+        <f>($H72/($F72*60))*3.6</f>
+        <v>8.28169014084507</v>
       </c>
       <c r="J72" s="6">
         <f>$H72/$G72</f>
-        <v>845.4545454545455</v>
+        <v>192.15686274509804</v>
       </c>
       <c r="K72" s="11">
-        <v>0.72299999999999998</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -3391,38 +3398,47 @@
       <c r="B73" t="s">
         <v>48</v>
       </c>
-      <c r="C73" s="2">
-        <v>503</v>
+      <c r="C73" s="14" t="s">
+        <v>62</v>
       </c>
       <c r="D73" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="E73" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F73">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="G73">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="H73">
-        <f>32.8*1000</f>
-        <v>32800</v>
+        <v>6500</v>
       </c>
       <c r="I73" s="3">
-        <f t="shared" si="2"/>
-        <v>24.599999999999998</v>
+        <f>($H73/($F73*60))*3.6</f>
+        <v>8.1250000000000018</v>
       </c>
       <c r="J73" s="6">
-        <f t="shared" ref="J73" si="4">$H73/$G73</f>
-        <v>780.95238095238096</v>
-      </c>
-      <c r="K73" s="13">
-        <v>0.82199999999999995</v>
+        <f>$H73/$G73</f>
+        <v>232.14285714285714</v>
+      </c>
+      <c r="K73" s="11">
+        <v>0.83399999999999996</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K73" xr:uid="{972E81A3-D75E-46E6-82F0-4D32CA77E236}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="PM Peak"/>
+      </filters>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A38:K73">
+      <sortCondition descending="1" ref="I1:I73"/>
+    </sortState>
+  </autoFilter>
   <conditionalFormatting sqref="B1:B1048576">
     <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Standard">
       <formula>NOT(ISERROR(SEARCH("Standard",B1)))</formula>
